--- a/r4-core-153-healthcareservice-profile/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-153-healthcareservice-profile/StructureDefinition-at-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3064" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3067" uniqueCount="429">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T21:21:27+00:00</t>
+    <t>2026-10-11T19:39:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -722,6 +722,12 @@
   </si>
   <si>
     <t>Practitioner.identifier:GDA-OID.type</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Practitioner.identifier:GDA-OID.system</t>
@@ -1073,6 +1079,10 @@
   </si>
   <si>
     <t>The home/mailing address of the practitioner is often required for employee administration purposes, and also for some rostering services where the start point (practitioners home) can be used in calculations.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+at-addr-1:If the extension for street name is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-streetName').empty() or $this.hasValue())}at-addr-2:If the extension for street number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-houseNumber').empty() or $this.hasValue())}at-addr-3:If the extension for floor/door number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-additionalLocator').empty() or $this.hasValue())}</t>
   </si>
   <si>
     <t>ORC-24, STF-11, ROL-11, PRT-14</t>
@@ -1675,7 +1685,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="51.97265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="46.58203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -4387,9 +4397,11 @@
       <c r="X24" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Y24" s="2"/>
+      <c r="Y24" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4436,7 +4448,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>187</v>
@@ -4465,7 +4477,7 @@
         <v>102</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M25" t="s" s="2">
         <v>189</v>
@@ -4481,7 +4493,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>21</v>
@@ -4552,7 +4564,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>197</v>
@@ -4581,7 +4593,7 @@
         <v>157</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M26" t="s" s="2">
         <v>199</v>
@@ -4666,7 +4678,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>206</v>
@@ -4778,7 +4790,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>214</v>
@@ -4892,10 +4904,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5004,10 +5016,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5118,10 +5130,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5147,13 +5159,13 @@
         <v>157</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5203,7 +5215,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5212,7 +5224,7 @@
         <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>100</v>
@@ -5232,10 +5244,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5261,13 +5273,13 @@
         <v>102</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5296,10 +5308,10 @@
         <v>183</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
@@ -5317,7 +5329,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5346,10 +5358,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5375,13 +5387,13 @@
         <v>146</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5431,7 +5443,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5449,7 +5461,7 @@
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
@@ -5460,10 +5472,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5489,13 +5501,13 @@
         <v>157</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5503,7 +5515,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>21</v>
@@ -5545,7 +5557,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5574,13 +5586,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>145</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>21</v>
@@ -5690,7 +5702,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>156</v>
@@ -5802,7 +5814,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>162</v>
@@ -5916,7 +5928,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>167</v>
@@ -6032,7 +6044,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>177</v>
@@ -6097,9 +6109,11 @@
       <c r="X39" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Y39" s="2"/>
+      <c r="Y39" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6146,7 +6160,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>187</v>
@@ -6175,7 +6189,7 @@
         <v>102</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M40" t="s" s="2">
         <v>189</v>
@@ -6191,7 +6205,7 @@
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>21</v>
@@ -6262,7 +6276,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>197</v>
@@ -6376,7 +6390,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>206</v>
@@ -6488,7 +6502,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>214</v>
@@ -6602,10 +6616,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6714,10 +6728,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6828,10 +6842,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6857,13 +6871,13 @@
         <v>157</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6913,7 +6927,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6922,7 +6936,7 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>100</v>
@@ -6942,10 +6956,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6971,13 +6985,13 @@
         <v>102</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7006,10 +7020,10 @@
         <v>183</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7027,7 +7041,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7056,10 +7070,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7085,13 +7099,13 @@
         <v>146</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7141,7 +7155,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7159,7 +7173,7 @@
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
@@ -7170,10 +7184,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7199,13 +7213,13 @@
         <v>157</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7213,7 +7227,7 @@
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>21</v>
@@ -7255,7 +7269,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7284,13 +7298,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>145</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>21</v>
@@ -7400,7 +7414,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>156</v>
@@ -7512,7 +7526,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>162</v>
@@ -7626,7 +7640,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>167</v>
@@ -7742,7 +7756,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>177</v>
@@ -7807,9 +7821,11 @@
       <c r="X54" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Y54" s="2"/>
+      <c r="Y54" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="Z54" t="s" s="2">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -7856,7 +7872,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>187</v>
@@ -7885,7 +7901,7 @@
         <v>102</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M55" t="s" s="2">
         <v>189</v>
@@ -7901,7 +7917,7 @@
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>21</v>
@@ -7972,7 +7988,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>197</v>
@@ -8086,7 +8102,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>206</v>
@@ -8198,7 +8214,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>214</v>
@@ -8312,10 +8328,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8424,10 +8440,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8538,10 +8554,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8567,13 +8583,13 @@
         <v>157</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8623,7 +8639,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8632,7 +8648,7 @@
         <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>100</v>
@@ -8652,10 +8668,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8681,13 +8697,13 @@
         <v>102</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8716,10 +8732,10 @@
         <v>183</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>21</v>
@@ -8737,7 +8753,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8766,10 +8782,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8795,13 +8811,13 @@
         <v>146</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8851,7 +8867,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8869,7 +8885,7 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>21</v>
@@ -8880,10 +8896,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8909,13 +8925,13 @@
         <v>157</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8923,7 +8939,7 @@
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>21</v>
@@ -8965,7 +8981,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8994,10 +9010,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9020,70 +9036,70 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q65" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="R65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="P65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q65" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="R65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9101,21 +9117,21 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9138,19 +9154,19 @@
         <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>21</v>
@@ -9199,7 +9215,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9214,13 +9230,13 @@
         <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -9228,10 +9244,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9254,19 +9270,19 @@
         <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>21</v>
@@ -9315,7 +9331,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9330,13 +9346,13 @@
         <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -9344,10 +9360,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9370,19 +9386,19 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -9431,7 +9447,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9443,16 +9459,16 @@
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>100</v>
+        <v>342</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -9460,10 +9476,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9489,14 +9505,14 @@
         <v>108</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -9524,10 +9540,10 @@
         <v>172</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>21</v>
@@ -9545,7 +9561,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9560,13 +9576,13 @@
         <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -9574,10 +9590,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9603,10 +9619,10 @@
         <v>157</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9686,10 +9702,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9715,10 +9731,10 @@
         <v>134</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9796,13 +9812,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="B72" t="s" s="2">
-        <v>355</v>
-      </c>
       <c r="C72" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>21</v>
@@ -9824,13 +9840,13 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9890,7 +9906,7 @@
         <v>79</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>139</v>
@@ -9910,10 +9926,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9939,10 +9955,10 @@
         <v>157</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9993,7 +10009,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10022,10 +10038,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10048,17 +10064,17 @@
         <v>89</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -10107,7 +10123,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10122,13 +10138,13 @@
         <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -10136,10 +10152,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10162,17 +10178,17 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -10221,7 +10237,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10239,10 +10255,10 @@
         <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
@@ -10250,10 +10266,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10276,13 +10292,13 @@
         <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10333,7 +10349,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10348,13 +10364,13 @@
         <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
@@ -10362,10 +10378,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10474,10 +10490,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10588,14 +10604,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -10617,10 +10633,10 @@
         <v>134</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>137</v>
@@ -10675,7 +10691,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10704,10 +10720,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10733,14 +10749,14 @@
         <v>146</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>21</v>
@@ -10789,7 +10805,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10807,7 +10823,7 @@
         <v>21</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>21</v>
@@ -10818,10 +10834,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10847,10 +10863,10 @@
         <v>178</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10877,31 +10893,31 @@
         <v>21</v>
       </c>
       <c r="X81" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF81" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>88</v>
@@ -10919,10 +10935,10 @@
         <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>21</v>
@@ -10930,10 +10946,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10959,14 +10975,14 @@
         <v>207</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>21</v>
@@ -11015,7 +11031,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11033,10 +11049,10 @@
         <v>21</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>21</v>
@@ -11044,10 +11060,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11073,10 +11089,10 @@
         <v>215</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11127,7 +11143,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11145,7 +11161,7 @@
         <v>21</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>21</v>
@@ -11156,10 +11172,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11185,16 +11201,16 @@
         <v>178</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
@@ -11243,7 +11259,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11258,13 +11274,13 @@
         <v>100</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>21</v>

--- a/r4-core-153-healthcareservice-profile/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-153-healthcareservice-profile/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-11T19:39:36+00:00</t>
+    <t>2026-10-12T11:53:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
